--- a/process/configuration/assets/output_data_dictionary.xlsx
+++ b/process/configuration/assets/output_data_dictionary.xlsx
@@ -484,7 +484,6 @@
           <t>Continent</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>category</t>
@@ -512,7 +511,6 @@
           <t>Country</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>category</t>
@@ -540,7 +538,6 @@
           <t>ISO 3166-1 alpha-2</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>category</t>
@@ -568,7 +565,6 @@
           <t>study_region</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>category</t>
@@ -948,7 +944,6 @@
           <t>grid_id</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>category</t>
@@ -976,7 +971,6 @@
           <t>point_id</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>category</t>
@@ -1036,9 +1030,6 @@
           <t>[destination]</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1056,8 +1047,6 @@
           <t>fresh_food_market</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>Food (strict)</t>
@@ -1080,8 +1069,6 @@
           <t>fresh_food_pooled</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>Food (lenient)</t>
@@ -1104,8 +1091,6 @@
           <t>convenience</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>Food</t>
@@ -1128,8 +1113,6 @@
           <t>public_open_space_large</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>Open space (strict)</t>
@@ -1152,8 +1135,6 @@
           <t>public_open_space_any</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>Open space (lenient)</t>
@@ -1168,16 +1149,14 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Large public green space (≥ 1 ha; OpenStreetMap and Earth Engine)</t>
+          <t>Public green space (OpenStreetMap and Earth Engine)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>large_public_green_space</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
+          <t>public_green_space</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>Open space</t>
@@ -1200,8 +1179,6 @@
           <t>pt_frequent</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>Transport (strict, cycling)</t>
@@ -1224,8 +1201,6 @@
           <t>pt_gtfs_freq_20</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>Transport (walking)</t>
@@ -1248,8 +1223,6 @@
           <t>pt_gtfs_freq_30</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>Transport (walking)</t>
@@ -1272,8 +1245,6 @@
           <t>pt_gtfs_any</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>Transport</t>
@@ -1296,8 +1267,6 @@
           <t>pt_osm_any</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>Transport</t>
@@ -1320,8 +1289,6 @@
           <t>pt_any</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>Transport (lenient)</t>
@@ -1344,8 +1311,6 @@
           <t>all_strict</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>Combined</t>
@@ -1368,8 +1333,6 @@
           <t>all_lenient</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>Combined</t>
@@ -1392,8 +1355,6 @@
           <t>activity_centre_local</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>Derived</t>
@@ -1416,8 +1377,6 @@
           <t>activity_centre_complete</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>Derived</t>
@@ -1435,10 +1394,6 @@
           <t>Regions can define their own destinations (custom OpenStreetMap tags or supplied datasets), pool categories, and configure additional combined-access sets and activity-centre definitions (a network location whose walkable catchment, default 400 m, contains at least one destination of every required category).  These follow the same naming patterns, e.g. all_&lt;set&gt;_&lt;variant&gt; for a named combined-access set and activity_centre_&lt;definition&gt;_&lt;tier&gt; for a named activity centre.  Combined-access composites have access indicators only (no nearest-distance variables).</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1456,9 +1411,6 @@
           <t>[x]</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1476,9 +1428,6 @@
           <t>[network]</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">

--- a/process/configuration/assets/output_data_dictionary.xlsx
+++ b/process/configuration/assets/output_data_dictionary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F86"/>
+  <dimension ref="A1:F87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -484,6 +484,7 @@
           <t>Continent</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>category</t>
@@ -511,6 +512,7 @@
           <t>Country</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>category</t>
@@ -538,6 +540,7 @@
           <t>ISO 3166-1 alpha-2</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>category</t>
@@ -565,6 +568,7 @@
           <t>study_region</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>category</t>
@@ -944,6 +948,7 @@
           <t>grid_id</t>
         </is>
       </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>category</t>
@@ -971,6 +976,7 @@
           <t>point_id</t>
         </is>
       </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>category</t>
@@ -1017,17 +1023,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Naming conventions and parameters</t>
+          <t>Analytical statistics</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The destination whose access is measured.  The default destinations are listed below.  Walking and cycling access draw on the same destination definitions, declared once in a region's "accessibility" configuration; each pairs a strict and a lenient variant of each core category (food, public open space, public transport) so that composite "all categories reachable" indicators can be derived per variant.</t>
+          <t>Count of areas of the aggregation summarised here that are associated with this area</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>[destination]</t>
+          <t>area_count</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>custom areas</t>
         </is>
       </c>
     </row>
@@ -1039,19 +1060,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Fresh food market / supermarket</t>
+          <t>The destination whose access is measured.  The default destinations are listed below.  Walking and cycling access draw on the same destination definitions, declared once in a region's "accessibility" configuration; each pairs a strict and a lenient variant of each core category (food, public open space, public transport) so that composite "all categories reachable" indicators can be derived per variant.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>fresh_food_market</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Food (strict)</t>
-        </is>
-      </c>
+          <t>[destination]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1061,17 +1080,19 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Fresh food, pooled (market, supermarket or convenience store)</t>
+          <t>Fresh food market / supermarket</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>fresh_food_pooled</t>
-        </is>
-      </c>
+          <t>fresh_food_market</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Food (lenient)</t>
+          <t>Food (strict)</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1104,19 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Convenience store</t>
+          <t>Fresh food, pooled (market, supermarket or convenience store)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>convenience</t>
-        </is>
-      </c>
+          <t>fresh_food_pooled</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Food (lenient)</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1128,19 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Large public open space (≥ 1.5 ha)</t>
+          <t>Convenience store</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>public_open_space_large</t>
-        </is>
-      </c>
+          <t>convenience</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Open space (strict)</t>
+          <t>Food</t>
         </is>
       </c>
     </row>
@@ -1127,17 +1152,19 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Any public open space</t>
+          <t>Large public open space (≥ 1.5 ha)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>public_open_space_any</t>
-        </is>
-      </c>
+          <t>public_open_space_large</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Open space (lenient)</t>
+          <t>Open space (strict)</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1176,19 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Public green space (OpenStreetMap and Earth Engine)</t>
+          <t>Any public open space</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>public_green_space</t>
-        </is>
-      </c>
+          <t>public_open_space_any</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Open space</t>
+          <t>Open space (lenient)</t>
         </is>
       </c>
     </row>
@@ -1171,17 +1200,19 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Frequent public transport (≤ 20 min daytime service; GTFS)</t>
+          <t>Public green space (OpenStreetMap and Earth Engine)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>pt_frequent</t>
-        </is>
-      </c>
+          <t>public_green_space</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Transport (strict, cycling)</t>
+          <t>Open space</t>
         </is>
       </c>
     </row>
@@ -1193,17 +1224,19 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Public transport, ≤ 20 min daytime service (GTFS)</t>
+          <t>Frequent public transport (≤ 20 min daytime service; GTFS)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>pt_gtfs_freq_20</t>
-        </is>
-      </c>
+          <t>pt_frequent</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Transport (walking)</t>
+          <t>Transport (strict, cycling)</t>
         </is>
       </c>
     </row>
@@ -1215,14 +1248,16 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Public transport, ≤ 30 min daytime service (GTFS)</t>
+          <t>Public transport, ≤ 20 min daytime service (GTFS)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>pt_gtfs_freq_30</t>
-        </is>
-      </c>
+          <t>pt_gtfs_freq_20</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>Transport (walking)</t>
@@ -1237,17 +1272,19 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Any public transport stop (GTFS)</t>
+          <t>Public transport, ≤ 30 min daytime service (GTFS)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>pt_gtfs_any</t>
-        </is>
-      </c>
+          <t>pt_gtfs_freq_30</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Transport (walking)</t>
         </is>
       </c>
     </row>
@@ -1259,14 +1296,16 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Any public transport stop (OpenStreetMap or custom)</t>
+          <t>Any public transport stop (GTFS)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>pt_osm_any</t>
-        </is>
-      </c>
+          <t>pt_gtfs_any</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>Transport</t>
@@ -1281,17 +1320,19 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Any public transport stop (best of GTFS and OpenStreetMap/custom)</t>
+          <t>Any public transport stop (OpenStreetMap or custom)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>pt_any</t>
-        </is>
-      </c>
+          <t>pt_osm_any</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Transport (lenient)</t>
+          <t>Transport</t>
         </is>
       </c>
     </row>
@@ -1303,17 +1344,19 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>All categories reachable, strict variants</t>
+          <t>Any public transport stop (best of GTFS and OpenStreetMap/custom)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>all_strict</t>
-        </is>
-      </c>
+          <t>pt_any</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Combined</t>
+          <t>Transport (lenient)</t>
         </is>
       </c>
     </row>
@@ -1325,14 +1368,16 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>All categories reachable, lenient variants</t>
+          <t>All categories reachable, strict variants</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>all_lenient</t>
-        </is>
-      </c>
+          <t>all_strict</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>Combined</t>
@@ -1347,17 +1392,19 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Local activity centre (everyday destinations co-located)</t>
+          <t>All categories reachable, lenient variants</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>activity_centre_local</t>
-        </is>
-      </c>
+          <t>all_lenient</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Derived</t>
+          <t>Combined</t>
         </is>
       </c>
     </row>
@@ -1369,14 +1416,16 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Complete activity centre (high-amenity destinations co-located)</t>
+          <t>Local activity centre (everyday destinations co-located)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>activity_centre_complete</t>
-        </is>
-      </c>
+          <t>activity_centre_local</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>Derived</t>
@@ -1391,7 +1440,19 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Regions can define their own destinations (custom OpenStreetMap tags or supplied datasets), pool categories, and configure additional combined-access sets and activity-centre definitions (a network location whose walkable catchment, default 400 m, contains at least one destination of every required category).  These follow the same naming patterns, e.g. all_&lt;set&gt;_&lt;variant&gt; for a named combined-access set and activity_centre_&lt;definition&gt;_&lt;tier&gt; for a named activity centre.  Combined-access composites have access indicators only (no nearest-distance variables).</t>
+          <t>Complete activity centre (high-amenity destinations co-located)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>activity_centre_complete</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Derived</t>
         </is>
       </c>
     </row>
@@ -1403,14 +1464,13 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Distance threshold (m).  Distances can be customised to locally policy-relevant values.  The core walking access indicators use the configured neighbourhood accessibility threshold (default 500 m).  Where a region configures the optional pedestrian accessibility analysis, walking access is additionally evaluated at each configured pedestrian distance, and cycling access at each configured cycling distance (defaults: 500 m, 1000 m, 2000 m and 5000 m), so an access variable exists for each distance.</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>[x]</t>
-        </is>
-      </c>
+          <t>Regions can define their own destinations (custom OpenStreetMap tags or supplied datasets), pool categories, and configure additional combined-access sets and activity-centre definitions (a network location whose walkable catchment, default 400 m, contains at least one destination of every required category).  These follow the same naming patterns, e.g. all_&lt;set&gt;_&lt;variant&gt; for a named combined-access set and activity_centre_&lt;definition&gt;_&lt;tier&gt; for a named activity centre.  Combined-access composites have access indicators only (no nearest-distance variables).</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1420,46 +1480,37 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Cycling route stress measure, appearing as an optional prefix on cycling variable names: "lts1_" for routes composed entirely of lowest-stress Level of Traffic Stress (LTS) 1 links (suitable for all ages and abilities); "safe_" for fully low-stress routes on LTS 1–2 links (the default headline measure); or no prefix for danger-weighted routing over the full cycling network (higher-stress links usable at a proportionate distance penalty).  Which measures are computed is configurable (cycling_indicators contrasts and measures settings).</t>
+          <t>Distance threshold (m).  Distances can be customised to locally policy-relevant values.  The core walking access indicators use the configured neighbourhood accessibility threshold (default 400 m).  Where a region configures the optional pedestrian accessibility analysis, walking access is additionally evaluated at each configured pedestrian distance, and cycling access at each configured cycling distance (defaults: 400 m, 1000 m, 2000 m and 5000 m), so an access variable exists for each distance.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>[network]</t>
-        </is>
-      </c>
+          <t>[x]</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Indicator estimates: access (walking)</t>
+          <t>Naming conventions and parameters</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Score (0-1) for walking access within the configured accessibility threshold distance (default 500 m) to the destination</t>
+          <t>Cycling route stress measure, appearing as an optional prefix on cycling variable names: "lts1_" for routes composed entirely of lowest-stress Level of Traffic Stress (LTS) 1 links (suitable for all ages and abilities); "safe_" for fully low-stress routes on LTS 1–2 links (the default headline measure); or no prefix for danger-weighted routing over the full cycling network (higher-stress links usable at a proportionate distance penalty).  Which measures are computed is configurable (cycling_indicators contrasts and measures settings).</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>sp_access_[destination]_score</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>score 0-1</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>sample point</t>
-        </is>
-      </c>
+          <t>[network]</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1469,17 +1520,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Distance (m) along the pedestrian network to the nearest destination</t>
+          <t>Score (0-1) for walking access within the configured accessibility threshold distance (default 400 m) to the destination</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>sp_nearest_node_[destination]</t>
+          <t>sp_access_[destination]_score</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>metres</t>
+          <t>score 0-1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1501,27 +1552,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Percentage of population with walking access within [x] m of the destination</t>
+          <t>Distance (m) along the pedestrian network to the nearest destination</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>pct_access_[x]m_[destination]_score</t>
+          <t>sp_nearest_node_[destination]</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>metres</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>percentage</t>
+          <t>value</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>grid, custom areas</t>
+          <t>sample point</t>
         </is>
       </c>
     </row>
@@ -1533,12 +1584,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Percentage of population with walking access within [x] m of the destination (population weighted)</t>
+          <t>Percentage of population with walking access within [x] m of the destination</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>pop_pct_access_[x]m_[destination]_score</t>
+          <t>pct_access_[x]m_[destination]_score</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1553,7 +1604,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>city, custom areas</t>
+          <t>grid, custom areas</t>
         </is>
       </c>
     </row>
@@ -1565,27 +1616,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Score (0/1): the destination is reachable within [x] m along the pedestrian network</t>
+          <t>Percentage of population with walking access within [x] m of the destination (population weighted)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>sp_walk_access_[destination]_[x]m</t>
+          <t>pop_pct_access_[x]m_[destination]_score</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>score 0-1</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>percentage</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>sample point</t>
+          <t>city, custom areas</t>
         </is>
       </c>
     </row>
@@ -1597,17 +1648,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Distance (m) along the pedestrian network to the nearest destination</t>
+          <t>Score (0/1): the destination is reachable within [x] m along the pedestrian network</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>sp_walk_nearest_node_[destination]</t>
+          <t>sp_walk_access_[destination]_[x]m</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>metres</t>
+          <t>score 0-1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1629,27 +1680,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Percentage of population with walking access within [x] m to the destination</t>
+          <t>Distance (m) along the pedestrian network to the nearest destination</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>pct_access_walk_[destination]_[x]m</t>
+          <t>sp_walk_nearest_node_[destination]</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>metres</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>percentage</t>
+          <t>value</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>grid, custom areas</t>
+          <t>sample point</t>
         </is>
       </c>
     </row>
@@ -1661,12 +1712,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Percentage of population with walking access within [x] m to the destination (population weighted)</t>
+          <t>Percentage of population with walking access within [x] m to the destination</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>pop_pct_access_walk_[destination]_[x]m</t>
+          <t>pct_access_walk_[destination]_[x]m</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1681,7 +1732,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>city, custom areas</t>
+          <t>grid, custom areas</t>
         </is>
       </c>
     </row>
@@ -1693,27 +1744,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Average distance (m) along the pedestrian network to the nearest destination</t>
+          <t>Percentage of population with walking access within [x] m to the destination (population weighted)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>avg_walk_dist_[destination]</t>
+          <t>pop_pct_access_walk_[destination]_[x]m</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>metres</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>mean</t>
+          <t>percentage</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>grid, custom areas</t>
+          <t>city, custom areas</t>
         </is>
       </c>
     </row>
@@ -1725,12 +1776,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Average distance (m) along the pedestrian network to the nearest destination (population weighted)</t>
+          <t>Average distance (m) along the pedestrian network to the nearest destination</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>pop_avg_walk_dist_[destination]</t>
+          <t>avg_walk_dist_[destination]</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1745,7 +1796,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>city, custom areas</t>
+          <t>grid, custom areas</t>
         </is>
       </c>
     </row>
@@ -1757,27 +1808,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Score (0/1): the nearest destination is further than [x] m along the pedestrian network</t>
+          <t>Average distance (m) along the pedestrian network to the nearest destination (population weighted)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>sp_walk_beyond_[destination]_[x]m</t>
+          <t>pop_avg_walk_dist_[destination]</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>score 0-1</t>
+          <t>metres</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>mean</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>sample point</t>
+          <t>city, custom areas</t>
         </is>
       </c>
     </row>
@@ -1789,27 +1840,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Percentage of population living further than [x] m along the pedestrian network from the nearest destination</t>
+          <t>Score (0/1): the nearest destination is further than [x] m along the pedestrian network</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>pct_beyond_walk_[destination]_[x]m</t>
+          <t>sp_walk_beyond_[destination]_[x]m</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>score 0-1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>percentage</t>
+          <t>value</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>grid, custom areas</t>
+          <t>sample point</t>
         </is>
       </c>
     </row>
@@ -1821,12 +1872,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Percentage of population living further than [x] m along the pedestrian network from the nearest destination (population weighted)</t>
+          <t>Percentage of population living further than [x] m along the pedestrian network from the nearest destination</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>pop_pct_beyond_walk_[destination]_[x]m</t>
+          <t>pct_beyond_walk_[destination]_[x]m</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1841,7 +1892,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>city, custom areas</t>
+          <t>grid, custom areas</t>
         </is>
       </c>
     </row>
@@ -1853,27 +1904,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Number of destinations of the sub-type reachable within [x] m along the pedestrian network</t>
+          <t>Percentage of population living further than [x] m along the pedestrian network from the nearest destination (population weighted)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>sp_walk_count_[set]__[sub-type]_[x]m</t>
+          <t>pop_pct_beyond_walk_[destination]_[x]m</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>percentage</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>sample point</t>
+          <t>city, custom areas</t>
         </is>
       </c>
     </row>
@@ -1885,12 +1936,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Average number of destinations of the sub-type reachable within [x] m along the pedestrian network</t>
+          <t>Number of destinations of the sub-type reachable within [x] m along the pedestrian network</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>avg_count_walk_[set]__[sub-type]_[x]m</t>
+          <t>sp_walk_count_[set]__[sub-type]_[x]m</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1900,12 +1951,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>mean</t>
+          <t>value</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>grid, custom areas</t>
+          <t>sample point</t>
         </is>
       </c>
     </row>
@@ -1917,27 +1968,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Diversity (0-1) of the sub-types reachable within [x] m along the pedestrian network: the Shannon entropy of the counts of each sub-type, normalised by the number of sub-types defined</t>
+          <t>Average number of destinations of the sub-type reachable within [x] m along the pedestrian network</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>sp_walk_diversity_[set]_[x]m</t>
+          <t>avg_count_walk_[set]__[sub-type]_[x]m</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>index 0-1</t>
+          <t>count</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>mean</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>sample point</t>
+          <t>grid, custom areas</t>
         </is>
       </c>
     </row>
@@ -1949,12 +2000,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Average diversity (0-1) of the sub-types reachable within [x] m along the pedestrian network</t>
+          <t>Diversity (0-1) of the sub-types reachable within [x] m along the pedestrian network: the Shannon entropy of the counts of each sub-type, normalised by the number of sub-types defined</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>avg_diversity_walk_[set]_[x]m</t>
+          <t>sp_walk_diversity_[set]_[x]m</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1964,12 +2015,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>mean</t>
+          <t>value</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>grid, custom areas</t>
+          <t>sample point</t>
         </is>
       </c>
     </row>
@@ -1981,12 +2032,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Share (0-1) of the set's sub-types with at least one destination reachable within [x] m along the pedestrian network</t>
+          <t>Average diversity (0-1) of the sub-types reachable within [x] m along the pedestrian network</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>sp_walk_richness_[set]_[x]m</t>
+          <t>avg_diversity_walk_[set]_[x]m</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1996,12 +2047,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>mean</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>sample point</t>
+          <t>grid, custom areas</t>
         </is>
       </c>
     </row>
@@ -2013,12 +2064,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Average share (0-1) of the set's sub-types with at least one destination reachable within [x] m along the pedestrian network</t>
+          <t>Share (0-1) of the set's sub-types with at least one destination reachable within [x] m along the pedestrian network</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>avg_richness_walk_[set]_[x]m</t>
+          <t>sp_walk_richness_[set]_[x]m</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2028,44 +2079,44 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>mean</t>
+          <t>value</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>grid, custom areas</t>
+          <t>sample point</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Indicator estimates: walkability</t>
+          <t>Indicator estimates: access (walking)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Average population density of the local walkable neighbourhood (population per km², based on the population grid cells intersecting the sample point neighbourhood)</t>
+          <t>Average share (0-1) of the set's sub-types with at least one destination reachable within [x] m along the pedestrian network</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>sp_local_nh_avg_pop_density</t>
+          <t>avg_richness_walk_[set]_[x]m</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>persons per km²</t>
+          <t>index 0-1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>mean</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>sample point</t>
+          <t>grid, custom areas</t>
         </is>
       </c>
     </row>
@@ -2077,17 +2128,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Average street intersection density of the local walkable neighbourhood (intersections per km²)</t>
+          <t>Average population density of the local walkable neighbourhood (population per km², based on the population grid cells intersecting the sample point neighbourhood)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>sp_local_nh_avg_intersection_density</t>
+          <t>sp_local_nh_avg_pop_density</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>count per km²</t>
+          <t>persons per km²</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2109,17 +2160,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Daily living score (/3): sum of access scores for fresh food, convenience and public transport destinations</t>
+          <t>Average street intersection density of the local walkable neighbourhood (intersections per km²)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>sp_daily_living_score</t>
+          <t>sp_local_nh_avg_intersection_density</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>score 0-3</t>
+          <t>count per km²</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2141,17 +2192,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Walkability index: sum of z-scores of the daily living score, neighbourhood population density and neighbourhood intersection density</t>
+          <t>Daily living score (/3): sum of access scores for fresh food, convenience and public transport destinations</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>sp_walkability_index</t>
+          <t>sp_daily_living_score</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>index (sum of z-scores)</t>
+          <t>score 0-3</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2173,27 +2224,27 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Average walkable neighbourhood population density (population per km²) of sample points in this area</t>
+          <t>Walkability index: sum of z-scores of the daily living score, neighbourhood population density and neighbourhood intersection density</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>local_nh_population_density</t>
+          <t>sp_walkability_index</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>persons per km²</t>
+          <t>index (sum of z-scores)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>mean</t>
+          <t>value</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>grid, city, custom areas</t>
+          <t>sample point</t>
         </is>
       </c>
     </row>
@@ -2205,17 +2256,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Average walkable neighbourhood intersection density (intersections per km²) of sample points in this area</t>
+          <t>Average walkable neighbourhood population density (population per km²) of sample points in this area</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>local_nh_intersection_density</t>
+          <t>local_nh_population_density</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>count per km²</t>
+          <t>persons per km²</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2237,17 +2288,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Average daily living score (/3) of sample points in this area</t>
+          <t>Average walkable neighbourhood intersection density (intersections per km²) of sample points in this area</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>local_daily_living</t>
+          <t>local_nh_intersection_density</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>score 0-3</t>
+          <t>count per km²</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2269,17 +2320,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Average walkability index of sample points in this area</t>
+          <t>Average daily living score (/3) of sample points in this area</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>local_walkability</t>
+          <t>local_daily_living</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>index (sum of z-scores)</t>
+          <t>score 0-3</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2301,17 +2352,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Average walkable neighbourhood population density (population per km²; population weighted)</t>
+          <t>Average walkability index of sample points in this area</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>pop_nh_pop_density</t>
+          <t>local_walkability</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>persons per km²</t>
+          <t>index (sum of z-scores)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2321,7 +2372,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>city, custom areas</t>
+          <t>grid, city, custom areas</t>
         </is>
       </c>
     </row>
@@ -2333,17 +2384,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Average walkable neighbourhood intersection density (intersections per km²; population weighted)</t>
+          <t>Average walkable neighbourhood population density (population per km²; population weighted)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>pop_nh_intersection_density</t>
+          <t>pop_nh_pop_density</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>count per km²</t>
+          <t>persons per km²</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2365,17 +2416,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Average daily living score (/3; population weighted)</t>
+          <t>Average walkable neighbourhood intersection density (intersections per km²; population weighted)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>pop_daily_living</t>
+          <t>pop_nh_intersection_density</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>score 0-3</t>
+          <t>count per km²</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2397,17 +2448,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Average walkability index (population weighted)</t>
+          <t>Average daily living score (/3; population weighted)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>pop_walkability</t>
+          <t>pop_daily_living</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>index (sum of z-scores)</t>
+          <t>score 0-3</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2424,22 +2475,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Indicator estimates: urban heat vulnerability</t>
+          <t>Indicator estimates: walkability</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Heat Exposure Index (HEI): the heat exposure sub-index, derived from land surface temperature</t>
+          <t>Average walkability index (population weighted)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>urban_heat_exposure_index</t>
+          <t>pop_walkability</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>index 0-100</t>
+          <t>index (sum of z-scores)</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2449,7 +2500,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>sample point, grid, city, custom areas</t>
+          <t>city, custom areas</t>
         </is>
       </c>
     </row>
@@ -2461,17 +2512,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Land surface temperature (°C): the temperature of the Earth’s surface, indicating the lived experience of heat (Landsat 8 surface reflectance, hottest third of the year)</t>
+          <t>Heat Exposure Index (HEI): the heat exposure sub-index, derived from land surface temperature</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>urban_heat_land_surface_temp_c</t>
+          <t>urban_heat_exposure_index</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>degrees Celsius</t>
+          <t>index 0-100</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2493,17 +2544,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Heat Sensitivity Index (HSI): the equally weighted heat sensitivity sub-index of land surface albedo, NDVI, NDBI, local climate zone, population density and vulnerable population</t>
+          <t>Land surface temperature (°C): the temperature of the Earth’s surface, indicating the lived experience of heat (Landsat 7/8/9 surface reflectance; hottest third of the year composited over the target year and four preceding years)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>urban_heat_sensitivity_index</t>
+          <t>urban_heat_land_surface_temp_c</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>index 0-100</t>
+          <t>degrees Celsius</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2525,17 +2576,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Land surface albedo: solar reflectance, where higher reflectance implies less surface heat retention (inverted, so that higher values indicate greater heat vulnerability)</t>
+          <t>Heat Sensitivity Index (HSI): the equally weighted heat sensitivity sub-index of land surface albedo, NDVI, NDBI, local climate zone, population density and vulnerable population</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>urban_heat_land_surface_albedo</t>
+          <t>urban_heat_sensitivity_index</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>proportion 0-1</t>
+          <t>index 0-100</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2557,17 +2608,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Normalised Difference Vegetation Index (NDVI): a spectral index of vegetation health and greenness (inverted, so that higher values indicate greater heat vulnerability)</t>
+          <t>Land surface albedo: solar reflectance, where higher reflectance implies less surface heat retention (inverted, so that higher values indicate greater heat vulnerability)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>urban_heat_ndvi</t>
+          <t>urban_heat_land_surface_albedo</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>index -1 to 1</t>
+          <t>proportion 0-1</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2589,12 +2640,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Normalised Difference Built-up Index (NDBI): a spectral index of impervious surfaces such as concrete and asphalt</t>
+          <t>Normalised Difference Vegetation Index (NDVI): a spectral index of vegetation health and greenness (inverted, so that higher values indicate greater heat vulnerability)</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>urban_heat_ndbi</t>
+          <t>urban_heat_ndvi</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2621,22 +2672,22 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Local Climate Zone: a standardised classification of land cover typologies for urban heat island studies, ordered from least heat retaining (water) to most heat retaining (bare rock or paved)</t>
+          <t>Normalised Difference Built-up Index (NDBI): a spectral index of impervious surfaces such as concrete and asphalt</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>urban_heat_local_climate_zone_ordered</t>
+          <t>urban_heat_ndbi</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>ordered class</t>
+          <t>index -1 to 1</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>mean</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -2653,22 +2704,22 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Population density (persons per km²), from the GHS-POP global human settlement population grid</t>
+          <t>Local Climate Zone: a standardised classification of land cover typologies for urban heat island studies, ordered from least heat retaining (water) to most heat retaining (bare rock or paved)</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>urban_heat_population_density_per_sqkm</t>
+          <t>urban_heat_local_climate_zone_ordered</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>persons per km²</t>
+          <t>ordered class</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>mean</t>
+          <t>category</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -2685,22 +2736,22 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Vulnerable population (%): those most at risk from heat on the basis of age, being the combined proportion of the population aged 0–4 and 65+ years</t>
+          <t>Population density (persons per km²), from the GHS-POP global human settlement population grid</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>urban_heat_vulnerable_pop_pct</t>
+          <t>urban_heat_population_density_per_sqkm</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>persons per km²</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>percentage</t>
+          <t>mean</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -2717,22 +2768,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Adaptive Capability Index (ACI): the equally weighted adaptive capability sub-index of child dependency ratio, subnational Human Development Index and infant mortality rate; higher values indicate lower adaptive capability</t>
+          <t>Vulnerable population (%): those most at risk from heat on the basis of age, being the combined proportion of the population aged 0–4 and 65+ years</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>urban_heat_adaptive_capability_index</t>
+          <t>urban_heat_vulnerable_pop_pct</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>index 0-100</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>mean</t>
+          <t>percentage</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -2749,17 +2800,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Child dependency ratio: children (aged 0–14 years) relative to the working age population (15–64 years), indicating economic reliance</t>
+          <t>Adaptive Capability Index (ACI): the equally weighted adaptive capability sub-index of child dependency ratio, subnational Human Development Index and infant mortality rate; higher values indicate lower adaptive capability</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>urban_heat_child_dependency_ratio</t>
+          <t>urban_heat_adaptive_capability_index</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ratio</t>
+          <t>index 0-100</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -2781,17 +2832,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Subnational Human Development Index: human well-being assessed through education, health and standard of living</t>
+          <t>Child dependency ratio: children (aged 0–14 years) relative to the working age population (15–64 years), indicating economic reliance</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>urban_heat_subnational_hdi</t>
+          <t>urban_heat_child_dependency_ratio</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>index 0-100</t>
+          <t>ratio</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -2813,17 +2864,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Infant mortality rate: deaths of children under 1 year of age per 1000 live births, a key indicator of population health</t>
+          <t>Subnational Human Development Index: human well-being assessed through education, health and standard of living</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>urban_heat_infant_mortality_rate</t>
+          <t>urban_heat_subnational_hdi</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>deaths per 1,000 live births</t>
+          <t>index 0-100</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -2845,17 +2896,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Global Urban Heat Vulnerability Index (GUHVI): the equally weighted composite of the Heat Exposure, Heat Sensitivity and Adaptive Capability indices, (HEI + HSI + ACI) / 3</t>
+          <t>Infant mortality rate: deaths of children under 1 year of age per 1000 live births, a key indicator of population health</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>urban_heat_guhvi</t>
+          <t>urban_heat_infant_mortality_rate</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>index 0-100</t>
+          <t>deaths per 1,000 live births</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -2877,22 +2928,22 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Global Urban Heat Vulnerability Index (GUHVI) class, from 1 (least vulnerable) to 5 (most vulnerable)</t>
+          <t>Global Urban Heat Vulnerability Index (GUHVI): the equally weighted composite of the Heat Exposure, Heat Sensitivity and Adaptive Capability indices, (HEI + HSI + ACI) / 3</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>urban_heat_guhvi_class</t>
+          <t>urban_heat_guhvi</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>class 1-5</t>
+          <t>index 0-100</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>mean</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -2909,25 +2960,57 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
+          <t>Global Urban Heat Vulnerability Index (GUHVI) class, from 1 (least vulnerable) to 5 (most vulnerable)</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>urban_heat_guhvi_class</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>class 1-5</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>sample point, grid, city, custom areas</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Indicator estimates: urban heat vulnerability</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
           <t>Percentage of population in Global Urban Heat Vulnerability Index (GUHVI) class 5, the most vulnerable class</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>pct_urban_heat_guhvi_class_5_most_vulnerable</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>percent</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="E87" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>grid, city, custom areas</t>
         </is>
